--- a/Homework 02 - WBS and Gantt Chart.xlsx
+++ b/Homework 02 - WBS and Gantt Chart.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a9c7c63b8d3e1e1c/School/4 - Info Sys Proj Mgmt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="428" documentId="11_F25DC773A252ABDACC1048EEF9187A645BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{944A01F4-9537-47D3-961F-8B84EF288DD0}"/>
+  <xr:revisionPtr revIDLastSave="438" documentId="11_F25DC773A252ABDACC1048EEF9187A645BDE58F3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38B46E25-FC71-4CBA-B2AD-F186B89A26E2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="WBS" sheetId="1" r:id="rId1"/>
@@ -93,9 +93,6 @@
     <t>Stakeholder Requirements</t>
   </si>
   <si>
-    <t>Competitve Analysis</t>
-  </si>
-  <si>
     <t>Vision and Scope</t>
   </si>
   <si>
@@ -363,9 +360,6 @@
     <t>Operator Training</t>
   </si>
   <si>
-    <t>System Adminstrator Handover</t>
-  </si>
-  <si>
     <t>Final Project Review</t>
   </si>
   <si>
@@ -409,6 +403,12 @@
   </si>
   <si>
     <t>*Project Timeline Gantt Chart (Days from September 1, 2026)</t>
+  </si>
+  <si>
+    <t>Competitive Analysis</t>
+  </si>
+  <si>
+    <t>System Administrator Handover</t>
   </si>
 </sst>
 </file>
@@ -440,37 +440,11 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -484,47 +458,9 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right/>
       <top/>
       <bottom style="thin">
@@ -543,51 +479,158 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1682,6 +1725,36 @@
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D29DF369-B930-4ABE-A294-E5083263C77B}" name="Table2" displayName="Table2" ref="C1:E68" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
+  <autoFilter ref="C1:E68" xr:uid="{D29DF369-B930-4ABE-A294-E5083263C77B}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{61658F72-BD87-41E8-84D8-3CC0BB2DEC7F}" name="CODE" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{92ED980F-21BC-4538-AA3D-D812CE04933A}" name="TASK" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{1F0040A8-923F-40C6-8248-E159096EBD48}" name="Parent Task" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{EC3CD1A4-43F2-429C-AE24-5ACB7406AA3F}" name="Table1" displayName="Table1" ref="A1:E13" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8">
+  <autoFilter ref="A1:E13" xr:uid="{EC3CD1A4-43F2-429C-AE24-5ACB7406AA3F}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{3AD66C97-7D34-4E0C-B17E-1E10B4C06286}" name="Task"/>
+    <tableColumn id="2" xr3:uid="{D8C294C9-1EF7-47DE-82F1-946B51157BB9}" name="Start" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{38A6044A-60B5-4DC5-B143-848CC64127EE}" name="Finish" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{3428B630-9943-4706-A261-3A1E0432D346}" name="Duration (days)">
+      <calculatedColumnFormula>C2-B2+1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{BE4F18AD-D5EA-457A-AE66-565109221F2B}" name="Start Offset">
+      <calculatedColumnFormula>B2-MIN($B$2:$B$13)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1945,765 +2018,769 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:H68"/>
+  <dimension ref="C1:I68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="39.5703125" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="39.5703125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="13.28515625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C1" s="1" t="s">
+    <row r="1" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C1" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="18" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C2" s="8">
+    <row r="2" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C2" s="11">
         <v>1</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C3" s="14">
+    <row r="3" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C3" s="12">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C4" s="15" t="s">
+    <row r="4" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C4" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="8">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C5" s="15" t="s">
+    <row r="5" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C6" s="12">
+        <v>1.2</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="3">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C6" s="14">
+      <c r="E6" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C7" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="8">
         <v>1.2</v>
       </c>
-      <c r="D6" t="s">
+      <c r="I7" s="5"/>
+    </row>
+    <row r="8" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C8" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C9" s="12">
+        <v>1.3</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E9" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C7" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
+    <row r="10" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C11" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="3">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C8" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="3">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C9" s="14">
+      <c r="E11" s="8">
         <v>1.3</v>
       </c>
-      <c r="D9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C12" s="13">
+        <v>2</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C13" s="12">
+        <v>2.1</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="16" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C16" s="12">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D16" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="3">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C11" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="3">
-        <v>1.3</v>
-      </c>
-      <c r="H11" s="16"/>
-    </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C12" s="11">
+      <c r="E16" s="8">
         <v>2</v>
       </c>
-      <c r="D12" s="12" t="s">
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C19" s="12">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C20" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C21" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E21" s="8">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C22" s="13">
         <v>3</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="D22" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C13" s="14">
-        <v>2.1</v>
-      </c>
-      <c r="D13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C14" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="3">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C15" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="3">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C16" s="14">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E16" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C17" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="3">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C18" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="3">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C19" s="14">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="D19" t="s">
-        <v>37</v>
-      </c>
-      <c r="E19" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C20" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" t="s">
-        <v>38</v>
-      </c>
-      <c r="E20" s="3">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C21" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" t="s">
+    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C23" s="12">
+        <v>3.1</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C24" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="3">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C22" s="11">
+      <c r="D24" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="8">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C26" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="8">
         <v>3</v>
       </c>
-      <c r="D22" s="12" t="s">
+    </row>
+    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C27" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" s="8">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="28" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C28" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="8">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C29" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E29" s="8">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="30" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C30" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C31" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="32" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C32" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E32" s="8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C33" s="12">
+        <v>3.4</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E33" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C34" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C35" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" s="8">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C36" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E36" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C37" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="8">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C38" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E38" s="8">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C39" s="13">
         <v>4</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="D39" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E39" s="15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C23" s="14">
-        <v>3.1</v>
-      </c>
-      <c r="D23" t="s">
-        <v>51</v>
-      </c>
-      <c r="E23" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C24" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="3">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C25" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D25" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="3">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="26" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C26" s="14">
-        <v>3.2</v>
-      </c>
-      <c r="D26" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C27" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="D27" t="s">
-        <v>55</v>
-      </c>
-      <c r="E27" s="3">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="28" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C28" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" t="s">
-        <v>56</v>
-      </c>
-      <c r="E28" s="3">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="29" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C29" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" t="s">
-        <v>57</v>
-      </c>
-      <c r="E29" s="3">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="30" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C30" s="14">
-        <v>3.3</v>
-      </c>
-      <c r="D30" t="s">
-        <v>58</v>
-      </c>
-      <c r="E30" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C31" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" t="s">
-        <v>59</v>
-      </c>
-      <c r="E31" s="3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="32" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C32" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" t="s">
-        <v>60</v>
-      </c>
-      <c r="E32" s="3">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C33" s="14">
-        <v>3.4</v>
-      </c>
-      <c r="D33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E33" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C34" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D34" t="s">
-        <v>62</v>
-      </c>
-      <c r="E34" s="3">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="35" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C35" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" t="s">
-        <v>63</v>
-      </c>
-      <c r="E35" s="3">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="36" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C36" s="14">
-        <v>3.5</v>
-      </c>
-      <c r="D36" t="s">
-        <v>64</v>
-      </c>
-      <c r="E36" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C37" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="D37" t="s">
-        <v>65</v>
-      </c>
-      <c r="E37" s="3">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="38" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C38" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D38" t="s">
+    <row r="40" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C40" s="12">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E40" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C41" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E38" s="3">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="39" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C39" s="11">
+      <c r="D41" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E41" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C42" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E42" s="8">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C43" s="12">
+        <v>4.2</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="E43" s="8">
         <v>4</v>
       </c>
-      <c r="D39" s="12" t="s">
+    </row>
+    <row r="44" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C44" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="E44" s="8">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C45" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E45" s="8">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C46" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E46" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C47" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" s="8">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="48" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C48" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" s="8">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C49" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E49" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C50" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E50" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="51" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C51" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E51" s="8">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="52" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C52" s="13">
         <v>5</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="D52" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E52" s="15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C40" s="14">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="D40" t="s">
-        <v>74</v>
-      </c>
-      <c r="E40" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C41" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="D41" t="s">
-        <v>75</v>
-      </c>
-      <c r="E41" s="3">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="42" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C42" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D42" t="s">
-        <v>76</v>
-      </c>
-      <c r="E42" s="3">
-        <v>4.0999999999999996</v>
-      </c>
-    </row>
-    <row r="43" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C43" s="14">
-        <v>4.2</v>
-      </c>
-      <c r="D43" t="s">
-        <v>77</v>
-      </c>
-      <c r="E43" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C44" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="D44" t="s">
-        <v>79</v>
-      </c>
-      <c r="E44" s="3">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="45" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C45" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D45" t="s">
-        <v>80</v>
-      </c>
-      <c r="E45" s="3">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="46" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C46" s="14">
-        <v>4.3</v>
-      </c>
-      <c r="D46" t="s">
-        <v>81</v>
-      </c>
-      <c r="E46" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C47" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="D47" t="s">
-        <v>82</v>
-      </c>
-      <c r="E47" s="3">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="48" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C48" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D48" t="s">
-        <v>83</v>
-      </c>
-      <c r="E48" s="3">
-        <v>4.3</v>
-      </c>
-    </row>
-    <row r="49" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C49" s="14">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="D49" t="s">
-        <v>84</v>
-      </c>
-      <c r="E49" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="50" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C50" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D50" t="s">
-        <v>85</v>
-      </c>
-      <c r="E50" s="3">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="51" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C51" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="D51" t="s">
+    <row r="53" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C53" s="12">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E53" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C54" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E51" s="3">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="52" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C52" s="11">
+      <c r="D54" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E54" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="55" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C55" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E55" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="56" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C56" s="12">
+        <v>5.2</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E56" s="8">
         <v>5</v>
       </c>
-      <c r="D52" s="12" t="s">
+    </row>
+    <row r="57" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C57" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E57" s="8">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="58" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C58" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E58" s="8">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="59" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C59" s="12">
+        <v>5.3</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E59" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C60" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E60" s="8">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C61" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E61" s="8">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="62" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C62" s="13">
         <v>6</v>
       </c>
-      <c r="E52" s="13" t="s">
+      <c r="D62" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E62" s="15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C53" s="14">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="D53" t="s">
-        <v>93</v>
-      </c>
-      <c r="E53" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C54" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D54" t="s">
-        <v>94</v>
-      </c>
-      <c r="E54" s="3">
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="55" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C55" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="D55" t="s">
-        <v>95</v>
-      </c>
-      <c r="E55" s="3">
-        <v>5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="56" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C56" s="14">
-        <v>5.2</v>
-      </c>
-      <c r="D56" t="s">
-        <v>96</v>
-      </c>
-      <c r="E56" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C57" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="D57" t="s">
-        <v>97</v>
-      </c>
-      <c r="E57" s="3">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="58" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C58" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D58" t="s">
-        <v>98</v>
-      </c>
-      <c r="E58" s="3">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="59" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C59" s="14">
-        <v>5.3</v>
-      </c>
-      <c r="D59" t="s">
+    <row r="63" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C63" s="12">
+        <v>6.1</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="E63" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C64" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E59" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="60" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C60" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D60" t="s">
-        <v>99</v>
-      </c>
-      <c r="E60" s="3">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="61" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C61" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="D61" t="s">
-        <v>100</v>
-      </c>
-      <c r="E61" s="3">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="62" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C62" s="11">
+      <c r="D64" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E64" s="8">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="65" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C65" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E65" s="8">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="66" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C66" s="12">
+        <v>6.2</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E66" s="8">
         <v>6</v>
       </c>
-      <c r="D62" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C63" s="14">
-        <v>6.1</v>
-      </c>
-      <c r="D63" t="s">
-        <v>106</v>
-      </c>
-      <c r="E63" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C64" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="D64" t="s">
-        <v>107</v>
-      </c>
-      <c r="E64" s="3">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="65" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C65" s="15" t="s">
+    </row>
+    <row r="67" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C67" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D67" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E65" s="3">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="66" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C66" s="14">
+      <c r="E67" s="8">
         <v>6.2</v>
       </c>
-      <c r="D66" t="s">
+    </row>
+    <row r="68" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C68" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="D68" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="E66" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="67" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C67" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="D67" t="s">
-        <v>110</v>
-      </c>
-      <c r="E67" s="3">
-        <v>6.2</v>
-      </c>
-    </row>
-    <row r="68" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C68" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E68" s="7">
+      <c r="E68" s="8">
         <v>6.2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -2715,263 +2792,266 @@
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
     <col min="2" max="2" width="14.28515625" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
     <col min="5" max="5" width="15.140625" customWidth="1"/>
     <col min="6" max="6" width="16.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="D1" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="E1" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="E1" s="18" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="19">
+      <c r="B2" s="4">
         <v>46266</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="4">
         <v>46283</v>
       </c>
       <c r="D2">
         <f>C2-B2+1</f>
         <v>18</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="9">
         <f>B2-MIN($B$2:$B$13)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B3" s="19">
+      <c r="A3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="4">
         <v>46279</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="4">
         <v>46295</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D13" si="0">C3-B3+1</f>
         <v>17</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3">
         <f t="shared" ref="E3:E13" si="1">B3-MIN($B$2:$B$13)</f>
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B4" s="19">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="4">
         <v>46286</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="4">
         <v>46297</v>
       </c>
       <c r="D4">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="19">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="4">
         <v>46296</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="4">
         <v>46311</v>
       </c>
       <c r="D5">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="19">
+      <c r="A6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="4">
         <v>46296</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="4">
         <v>46318</v>
       </c>
       <c r="D6">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B7" s="19">
+      <c r="A7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="4">
         <v>46307</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="4">
         <v>46325</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="19">
+      <c r="A8" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="4">
         <v>46307</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="4">
         <v>46325</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B9" s="19">
+      <c r="A9" t="s">
+        <v>118</v>
+      </c>
+      <c r="B9" s="4">
         <v>46314</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="4">
         <v>46332</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="19">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" s="4">
         <v>46328</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="4">
         <v>46339</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10">
         <f t="shared" si="1"/>
         <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11" s="19">
+      <c r="A11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B11" s="4">
         <v>46335</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="4">
         <v>46351</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11">
         <f t="shared" si="1"/>
         <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="19">
+      <c r="B12" s="4">
         <v>46356</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="4">
         <v>46360</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12">
         <f t="shared" si="1"/>
         <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="20">
+      <c r="B13" s="4">
         <v>46363</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="4">
         <v>46367</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13">
         <f t="shared" si="1"/>
         <v>97</v>
       </c>
     </row>
     <row r="23" spans="7:7" x14ac:dyDescent="0.25">
       <c r="G23" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>